--- a/docs/telephony/HRX-Telephony-UAT.xlsx
+++ b/docs/telephony/HRX-Telephony-UAT.xlsx
@@ -715,14 +715,14 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>HRX × CentroVision — Telephony Integration UAT</t>
+          <t>HRX — Telephony Integration UAT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Hi Tech Group · hrx.hitechgroup.in · CentroVision 3.0 dialer / GSM gateway</t>
+          <t>Hi Tech Group · hrx.hitechgroup.in · vendor dialer / GSM gateway</t>
         </is>
       </c>
     </row>
@@ -757,14 +757,14 @@
     <row r="10" ht="28" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Vendor Questionnaire — The 15 questions CentroVision answers IN WRITING before the SOW is signed. Vague answers here become change requests later.</t>
+          <t>Vendor Questionnaire — The 15 questions the vendor answers IN WRITING before the SOW is signed. Vague answers here become change requests later.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Field Confirmation — Field by field, what CentroVision can and cannot supply. Anything marked No or Partial must be agreed before UAT, not discovered during it.</t>
+          <t>Field Confirmation — Field by field, what the vendor can and cannot supply. Anything marked No or Partial must be agreed before UAT, not discovered during it.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
     <row r="23" ht="42" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Companion files: hrms-telephony-webhook-v1.yaml · centrovision-required-v1.yaml · HRX-Telephony.postman_collection.json</t>
+          <t>Companion files: hrms-telephony-webhook-v1.yaml · vendor-required-v1.yaml · HRX-Telephony.postman_collection.json</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Expected on CentroVision</t>
+          <t>Expected on vendor platform</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>CentroVision's answer</t>
+          <t>Vendor's answer</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>CentroVision calls</t>
+          <t>Vendor calls</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -3560,7 +3560,7 @@
     <row r="20">
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>CentroVision — name, signature, date</t>
+          <t>Vendor — name, signature, date</t>
         </is>
       </c>
       <c r="C20" s="40" t="n"/>
